--- a/data/trans_camb/IP1016-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1016-Clase-trans_camb.xlsx
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,73</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,29</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,26</t>
+          <t>0,0; 0,32</t>
         </is>
       </c>
     </row>
